--- a/data/raw/medicamentos.xlsx
+++ b/data/raw/medicamentos.xlsx
@@ -574,11 +574,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>678319200000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1699460637000</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>08/11/23</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -667,11 +671,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>880930800000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1699460638000</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30/11/97</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>08/11/23</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -760,11 +768,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>678319200000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1699460630000</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>08/11/23</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -853,8 +865,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>-213152400000</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>31/03/63</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -944,8 +958,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>1178488800000</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>06/05/07</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -1035,8 +1051,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>1178488800000</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>06/05/07</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
@@ -1126,8 +1144,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>1425337200000</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>02/03/15</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
@@ -1217,8 +1237,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>1425337200000</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>02/03/15</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -1308,8 +1330,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>1188856800000</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>03/09/07</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
@@ -1399,8 +1423,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>1188856800000</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>03/09/07</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
@@ -1490,8 +1516,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>1464624600000</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30/05/16</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -1581,8 +1609,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>1464559200000</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>29/05/16</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
@@ -1672,8 +1702,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>1468965600000</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>19/07/16</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
@@ -1763,8 +1795,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>1468965600000</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>19/07/16</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
@@ -1854,8 +1888,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>1480892400000</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>04/12/16</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
@@ -1945,8 +1981,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>1480892400000</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>04/12/16</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
@@ -2036,8 +2074,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>1015801200000</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10/03/02</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
@@ -2127,8 +2167,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>1015801200000</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10/03/02</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
@@ -2218,8 +2260,10 @@
           <t>COLIRIO DE LIBERACION PROLONGADA</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>1096322400000</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>27/09/04</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
@@ -2309,8 +2353,10 @@
           <t>COLIRIO DE LIBERACION PROLONGADA</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>1096322400000</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>27/09/04</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
@@ -2400,8 +2446,10 @@
           <t>COLIRIO DE LIBERACION PROLONGADA</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>1269385200000</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23/03/10</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
@@ -2491,8 +2539,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>1298242800000</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
@@ -2582,8 +2632,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>1298242800000</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
@@ -2673,8 +2725,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>1298242800000</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
@@ -2764,8 +2818,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>1298242800000</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
@@ -2855,8 +2911,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>1298242800000</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20/02/11</t>
+        </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -2946,8 +3004,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>1222380000000</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25/09/08</t>
+        </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
@@ -3037,8 +3097,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>1222380000000</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25/09/08</t>
+        </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -3128,8 +3190,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>1222380000000</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25/09/08</t>
+        </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
@@ -3219,8 +3283,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>1048546800000</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>24/03/03</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
@@ -3310,8 +3376,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>1048114800000</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>19/03/03</t>
+        </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
@@ -3401,8 +3469,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>1302732000000</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>13/04/11</t>
+        </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
@@ -3492,8 +3562,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>372034800000</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15/10/81</t>
+        </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
@@ -3583,8 +3655,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>497574000000</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>07/10/85</t>
+        </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
@@ -3674,8 +3748,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>1443105399000</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>24/09/15</t>
+        </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
@@ -3765,8 +3841,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>1443105401000</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>24/09/15</t>
+        </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
@@ -3856,11 +3934,15 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>1287957600000</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1696403843000</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>24/10/10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>04/10/23</t>
+        </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3949,8 +4031,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>1359933061000</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
@@ -4040,8 +4124,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>1359933044000</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
@@ -4131,8 +4217,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>1359933041000</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
@@ -4222,8 +4310,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I42" t="n">
-        <v>1359933037000</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>03/02/13</t>
+        </is>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
@@ -4313,8 +4403,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>1452770196000</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
@@ -4404,8 +4496,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>1452770194000</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
@@ -4495,8 +4589,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>1452770197000</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
@@ -4586,8 +4682,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>1312408800000</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>03/08/11</t>
+        </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
@@ -4677,8 +4775,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I47" t="n">
-        <v>1312408800000</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>03/08/11</t>
+        </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
@@ -4768,8 +4868,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>1312322400000</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>02/08/11</t>
+        </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
@@ -4859,8 +4961,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>959551200000</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>28/05/00</t>
+        </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -4932,7 +5036,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Viatris Pharmaceuticals S.L.U.</t>
+          <t>Viatris Pharmaceuticals S.L.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4950,8 +5054,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>925509600000</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30/04/99</t>
+        </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
@@ -5023,7 +5129,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Viatris Pharmaceuticals S.L.U.</t>
+          <t>Viatris Pharmaceuticals S.L.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5041,8 +5147,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>925509600000</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30/04/99</t>
+        </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
@@ -5132,8 +5240,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>1105484400000</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>11/01/05</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
@@ -5223,8 +5333,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I53" t="n">
-        <v>1215381600000</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>06/07/08</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
@@ -5314,8 +5426,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I54" t="n">
-        <v>1069110000000</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17/11/03</t>
+        </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
@@ -5405,8 +5519,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>1215381600000</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>06/07/08</t>
+        </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -5496,8 +5612,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I56" t="n">
-        <v>907192800000</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>30/09/98</t>
+        </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
@@ -5587,8 +5705,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I57" t="n">
-        <v>1111446000000</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>21/03/05</t>
+        </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
@@ -5678,8 +5798,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I58" t="n">
-        <v>1232492400000</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20/01/09</t>
+        </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -5769,8 +5891,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I59" t="n">
-        <v>1069110000000</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>17/11/03</t>
+        </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -5860,8 +5984,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I60" t="n">
-        <v>1232492400000</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20/01/09</t>
+        </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -5951,11 +6077,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>646783200000</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1753108997000</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30/06/90</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>21/07/25</t>
+        </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6044,8 +6174,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>1369951200000</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30/05/13</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
@@ -6135,8 +6267,10 @@
           <t>CAPSULA LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>1369951200000</v>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30/05/13</t>
+        </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
@@ -6226,8 +6360,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>641512800000</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30/04/90</t>
+        </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
@@ -6317,8 +6453,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>730940400000</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>28/02/93</t>
+        </is>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
@@ -6408,8 +6546,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I66" t="n">
-        <v>1188424800000</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>29/08/07</t>
+        </is>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
@@ -6499,8 +6639,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I67" t="n">
-        <v>1336428000000</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>07/05/12</t>
+        </is>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
@@ -6590,8 +6732,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>1154037600000</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>27/07/06</t>
+        </is>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
@@ -6681,8 +6825,10 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>1326668400000</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>15/01/12</t>
+        </is>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
@@ -6772,8 +6918,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I70" t="n">
-        <v>673048800000</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>30/04/91</t>
+        </is>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
@@ -6863,8 +7011,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>979772400000</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>17/01/01</t>
+        </is>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
@@ -6954,11 +7104,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I72" t="n">
-        <v>963784800000</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1768393391000</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>16/07/00</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>14/01/26</t>
+        </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -7047,8 +7201,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I73" t="n">
-        <v>928188000000</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>31/05/99</t>
+        </is>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
@@ -7138,8 +7294,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I74" t="n">
-        <v>928188000000</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>31/05/99</t>
+        </is>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
@@ -7229,8 +7387,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I75" t="n">
-        <v>1065564000000</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>07/10/03</t>
+        </is>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
@@ -7320,8 +7480,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I76" t="n">
-        <v>1300316400000</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>16/03/11</t>
+        </is>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
@@ -7411,8 +7573,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I77" t="n">
-        <v>1213826400000</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>18/06/08</t>
+        </is>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
@@ -7502,8 +7666,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I78" t="n">
-        <v>1038956400000</v>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>03/12/02</t>
+        </is>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
@@ -7593,8 +7759,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I79" t="n">
-        <v>1315260000000</v>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>05/09/11</t>
+        </is>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
@@ -7684,8 +7852,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>1454540400000</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>03/02/16</t>
+        </is>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
@@ -7731,7 +7901,7 @@
         <v>1</v>
       </c>
       <c r="W80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -7775,8 +7945,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>1454540400000</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>03/02/16</t>
+        </is>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
@@ -7822,7 +7994,7 @@
         <v>1</v>
       </c>
       <c r="W81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -7866,8 +8038,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I82" t="n">
-        <v>1306965600000</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>01/06/11</t>
+        </is>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
@@ -7957,8 +8131,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>1306965600000</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>01/06/11</t>
+        </is>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
@@ -8048,8 +8224,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>1317765600000</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>04/10/11</t>
+        </is>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
@@ -8139,8 +8317,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>1386802800000</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>11/12/13</t>
+        </is>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
@@ -8230,8 +8410,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I86" t="n">
-        <v>1145570400000</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20/04/06</t>
+        </is>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
@@ -8321,8 +8503,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>1145484000000</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>19/04/06</t>
+        </is>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
@@ -8412,8 +8596,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>1283724000000</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>05/09/10</t>
+        </is>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
@@ -8503,8 +8689,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>1286316000000</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>05/10/10</t>
+        </is>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
@@ -8594,8 +8782,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>1114552800000</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>26/04/05</t>
+        </is>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
@@ -8685,8 +8875,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>1221602400000</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>16/09/08</t>
+        </is>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
@@ -8776,8 +8968,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>1076281200000</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>08/02/04</t>
+        </is>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
@@ -8867,8 +9061,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>928188000000</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>31/05/99</t>
+        </is>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
@@ -8958,11 +9154,15 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>1303855200000</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1661785719000</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>26/04/11</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>29/08/22</t>
+        </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -9051,8 +9251,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>1266274800000</v>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>15/02/10</t>
+        </is>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
@@ -9142,11 +9344,15 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>1424369353000</v>
-      </c>
-      <c r="J96" t="n">
-        <v>1661785637000</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>19/02/15</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>29/08/22</t>
+        </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -9235,8 +9441,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>1263423600000</v>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>13/01/10</t>
+        </is>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
@@ -9326,8 +9534,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>1263423600000</v>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>13/01/10</t>
+        </is>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
@@ -9417,8 +9627,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>1213653600000</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>16/06/08</t>
+        </is>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
@@ -9508,8 +9720,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>1213653600000</v>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>16/06/08</t>
+        </is>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
@@ -9599,11 +9813,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>1073862000000</v>
-      </c>
-      <c r="J101" t="n">
-        <v>1640075969000</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>11/01/04</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>21/12/21</t>
+        </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -9692,8 +9910,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>996703200000</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>01/08/01</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
@@ -9783,8 +10003,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>996703200000</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>01/08/01</t>
+        </is>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
@@ -9874,8 +10096,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>1248386400000</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>23/07/09</t>
+        </is>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
@@ -9965,8 +10189,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>1248300000000</v>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>22/07/09</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
@@ -10056,8 +10282,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>867708000000</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>30/06/97</t>
+        </is>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
@@ -10147,11 +10375,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>1144360800000</v>
-      </c>
-      <c r="J107" t="n">
-        <v>1730820306000</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>06/04/06</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>05/11/24</t>
+        </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -10240,11 +10472,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I108" t="n">
-        <v>1144360800000</v>
-      </c>
-      <c r="J108" t="n">
-        <v>1730820305000</v>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>06/04/06</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>05/11/24</t>
+        </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -10333,8 +10569,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I109" t="n">
-        <v>1202770800000</v>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>11/02/08</t>
+        </is>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
@@ -10424,8 +10662,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I110" t="n">
-        <v>1202770800000</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>11/02/08</t>
+        </is>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
@@ -10515,8 +10755,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I111" t="n">
-        <v>1183068000000</v>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>28/06/07</t>
+        </is>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
@@ -10606,8 +10848,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I112" t="n">
-        <v>1183068000000</v>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>28/06/07</t>
+        </is>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
@@ -10697,8 +10941,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I113" t="n">
-        <v>1291071600000</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>29/11/10</t>
+        </is>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
@@ -10788,8 +11034,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>1216245600000</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>16/07/08</t>
+        </is>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
@@ -10879,8 +11127,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I115" t="n">
-        <v>1216245600000</v>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>16/07/08</t>
+        </is>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
@@ -10970,11 +11220,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I116" t="n">
-        <v>1300834800000</v>
-      </c>
-      <c r="J116" t="n">
-        <v>1731320161000</v>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>22/03/11</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>11/11/24</t>
+        </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -11063,11 +11317,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>1300834800000</v>
-      </c>
-      <c r="J117" t="n">
-        <v>1729003024000</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>22/03/11</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>15/10/24</t>
+        </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -11156,8 +11414,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I118" t="n">
-        <v>1295996400000</v>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>25/01/11</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
@@ -11247,8 +11507,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>1295996400000</v>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>25/01/11</t>
+        </is>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
@@ -11338,8 +11600,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>1296082800000</v>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>26/01/11</t>
+        </is>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -11429,8 +11693,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I121" t="n">
-        <v>1296082800000</v>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>26/01/11</t>
+        </is>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
@@ -11520,11 +11786,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I122" t="n">
-        <v>1114725600000</v>
-      </c>
-      <c r="J122" t="n">
-        <v>1637593801000</v>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>28/04/05</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>22/11/21</t>
+        </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -11532,7 +11802,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
         <v>1</v>
@@ -11613,11 +11883,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I123" t="n">
-        <v>1075935600000</v>
-      </c>
-      <c r="J123" t="n">
-        <v>1637593802000</v>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>04/02/04</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>22/11/21</t>
+        </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -11625,7 +11899,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
         <v>1</v>
@@ -11706,8 +11980,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>1349871741000</v>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>10/10/12</t>
+        </is>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
@@ -11797,11 +12073,15 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="I125" t="n">
-        <v>880930800000</v>
-      </c>
-      <c r="J125" t="n">
-        <v>1636995048000</v>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>30/11/97</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>15/11/21</t>
+        </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -11890,8 +12170,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I126" t="n">
-        <v>1460477260000</v>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>12/04/16</t>
+        </is>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
@@ -11981,8 +12263,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I127" t="n">
-        <v>1460477259000</v>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>12/04/16</t>
+        </is>
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
@@ -12072,8 +12356,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I128" t="n">
-        <v>1460477258000</v>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>12/04/16</t>
+        </is>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
@@ -12163,11 +12449,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I129" t="n">
-        <v>1485471600000</v>
-      </c>
-      <c r="J129" t="n">
-        <v>1660205385000</v>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>26/01/17</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>11/08/22</t>
+        </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -12256,11 +12546,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>1485471600000</v>
-      </c>
-      <c r="J130" t="n">
-        <v>1660205588000</v>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>26/01/17</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>11/08/22</t>
+        </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -12349,11 +12643,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I131" t="n">
-        <v>1485471600000</v>
-      </c>
-      <c r="J131" t="n">
-        <v>1660205308000</v>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>26/01/17</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>11/08/22</t>
+        </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -12442,8 +12740,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I132" t="n">
-        <v>1449840583000</v>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>11/12/15</t>
+        </is>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
@@ -12533,8 +12833,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>1449840594000</v>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>11/12/15</t>
+        </is>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
@@ -12624,8 +12926,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I134" t="n">
-        <v>1479285533000</v>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>16/11/16</t>
+        </is>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
@@ -12715,8 +13019,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I135" t="n">
-        <v>1479250800000</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>15/11/16</t>
+        </is>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
@@ -12806,8 +13112,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I136" t="n">
-        <v>1479285514000</v>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>16/11/16</t>
+        </is>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
@@ -12897,8 +13205,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>1479285505000</v>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>16/11/16</t>
+        </is>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
@@ -12988,11 +13298,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>1452770176000</v>
-      </c>
-      <c r="J138" t="n">
-        <v>1659948764000</v>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -13081,11 +13395,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>1452770182000</v>
-      </c>
-      <c r="J139" t="n">
-        <v>1659948770000</v>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -13174,11 +13492,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>1452770180000</v>
-      </c>
-      <c r="J140" t="n">
-        <v>1659948776000</v>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -13267,11 +13589,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>1452770179000</v>
-      </c>
-      <c r="J141" t="n">
-        <v>1659948776000</v>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>14/01/16</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>08/08/22</t>
+        </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -13360,8 +13686,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>899244000000</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>30/06/98</t>
+        </is>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
@@ -13451,8 +13779,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>899244000000</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>30/06/98</t>
+        </is>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
@@ -13542,8 +13872,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I144" t="n">
-        <v>899244000000</v>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>30/06/98</t>
+        </is>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
@@ -13633,8 +13965,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I145" t="n">
-        <v>1273615200000</v>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
@@ -13724,8 +14058,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I146" t="n">
-        <v>1273615200000</v>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
@@ -13815,8 +14151,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I147" t="n">
-        <v>1273615200000</v>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
@@ -13906,8 +14244,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I148" t="n">
-        <v>1273615200000</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>11/05/10</t>
+        </is>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
@@ -13997,8 +14337,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I149" t="n">
-        <v>1392228617000</v>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>12/02/14</t>
+        </is>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
@@ -14088,8 +14430,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I150" t="n">
-        <v>728521200000</v>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>31/01/93</t>
+        </is>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
@@ -14179,8 +14523,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I151" t="n">
-        <v>678319200000</v>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
@@ -14270,8 +14616,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I152" t="n">
-        <v>678319200000</v>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>30/06/91</t>
+        </is>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
@@ -14361,8 +14709,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I153" t="n">
-        <v>1288738800000</v>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>02/11/10</t>
+        </is>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
@@ -14452,8 +14802,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I154" t="n">
-        <v>1288738800000</v>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>02/11/10</t>
+        </is>
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
@@ -14525,7 +14877,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Guidotti Farma S.L.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -14543,8 +14895,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I155" t="n">
-        <v>1248127200000</v>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>20/07/09</t>
+        </is>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
@@ -14616,7 +14970,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Guidotti Farma S.L.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -14634,8 +14988,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I156" t="n">
-        <v>1248127200000</v>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>20/07/09</t>
+        </is>
       </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
@@ -14707,7 +15063,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Guidotti Farma S.L.</t>
+          <t>Laboratorios Menarini S.A.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -14725,8 +15081,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I157" t="n">
-        <v>950050800000</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>08/02/00</t>
+        </is>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
@@ -14816,8 +15174,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I158" t="n">
-        <v>1437516000000</v>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>21/07/15</t>
+        </is>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
@@ -14907,8 +15267,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I159" t="n">
-        <v>1308607200000</v>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>20/06/11</t>
+        </is>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
@@ -14998,8 +15360,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I160" t="n">
-        <v>1308607200000</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>20/06/11</t>
+        </is>
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
@@ -15089,8 +15453,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I161" t="n">
-        <v>1308607200000</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>20/06/11</t>
+        </is>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
@@ -15180,8 +15546,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I162" t="n">
-        <v>1352191158000</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>06/11/12</t>
+        </is>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
@@ -15271,8 +15639,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I163" t="n">
-        <v>1352191156000</v>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>06/11/12</t>
+        </is>
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
@@ -15362,8 +15732,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I164" t="n">
-        <v>1334440800000</v>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>14/04/12</t>
+        </is>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
@@ -15453,11 +15825,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I165" t="n">
-        <v>1383079311000</v>
-      </c>
-      <c r="J165" t="n">
-        <v>1678703511000</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>29/10/13</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>13/03/23</t>
+        </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -15546,11 +15922,15 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I166" t="n">
-        <v>1383079304000</v>
-      </c>
-      <c r="J166" t="n">
-        <v>1678703520000</v>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>29/10/13</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>13/03/23</t>
+        </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -15639,8 +16019,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I167" t="n">
-        <v>197157600000</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>31/03/76</t>
+        </is>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
@@ -15730,8 +16112,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I168" t="n">
-        <v>323391600000</v>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>31/03/80</t>
+        </is>
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
@@ -15821,8 +16205,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>323391600000</v>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>31/03/80</t>
+        </is>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
@@ -15912,8 +16298,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I170" t="n">
-        <v>1133391600000</v>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>30/11/05</t>
+        </is>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
@@ -16003,8 +16391,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I171" t="n">
-        <v>1133391600000</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>30/11/05</t>
+        </is>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
@@ -16094,8 +16484,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I172" t="n">
-        <v>1133391600000</v>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>30/11/05</t>
+        </is>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
@@ -16185,8 +16577,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I173" t="n">
-        <v>1095285600000</v>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>15/09/04</t>
+        </is>
       </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
@@ -16276,8 +16670,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I174" t="n">
-        <v>1095285600000</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>15/09/04</t>
+        </is>
       </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
@@ -16367,8 +16763,10 @@
           <t>COLIRIO</t>
         </is>
       </c>
-      <c r="I175" t="n">
-        <v>833580000000</v>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>31/05/96</t>
+        </is>
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
@@ -16458,8 +16856,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I176" t="n">
-        <v>1010012400000</v>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>02/01/02</t>
+        </is>
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
@@ -16549,8 +16949,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I177" t="n">
-        <v>1193004000000</v>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>21/10/07</t>
+        </is>
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
@@ -16640,8 +17042,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I178" t="n">
-        <v>1010012400000</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>02/01/02</t>
+        </is>
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
@@ -16731,8 +17135,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>1276725600000</v>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>16/06/10</t>
+        </is>
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
@@ -16822,8 +17228,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I180" t="n">
-        <v>1295564400000</v>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>20/01/11</t>
+        </is>
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
@@ -16913,8 +17321,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I181" t="n">
-        <v>1276725600000</v>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>16/06/10</t>
+        </is>
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
@@ -17004,8 +17414,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I182" t="n">
-        <v>1289948400000</v>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>16/11/10</t>
+        </is>
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
@@ -17095,8 +17507,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I183" t="n">
-        <v>1289948400000</v>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>16/11/10</t>
+        </is>
       </c>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
@@ -17186,8 +17600,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I184" t="n">
-        <v>1295910000000</v>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>24/01/11</t>
+        </is>
       </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
@@ -17277,8 +17693,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I185" t="n">
-        <v>1295910000000</v>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>24/01/11</t>
+        </is>
       </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
@@ -17368,8 +17786,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I186" t="n">
-        <v>1325026800000</v>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>27/12/11</t>
+        </is>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
@@ -17459,8 +17879,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I187" t="n">
-        <v>1325026800000</v>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>27/12/11</t>
+        </is>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
@@ -17550,8 +17972,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I188" t="n">
-        <v>1295910000000</v>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>24/01/11</t>
+        </is>
       </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
@@ -17641,8 +18065,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I189" t="n">
-        <v>441759600000</v>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>31/12/83</t>
+        </is>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
@@ -17732,8 +18158,10 @@
           <t>CAPSULA</t>
         </is>
       </c>
-      <c r="I190" t="n">
-        <v>644191200000</v>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>31/05/90</t>
+        </is>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
@@ -17823,8 +18251,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I191" t="n">
-        <v>1436824800000</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>13/07/15</t>
+        </is>
       </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
@@ -17914,8 +18344,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I192" t="n">
-        <v>1436824800000</v>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>13/07/15</t>
+        </is>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
@@ -18005,8 +18437,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I193" t="n">
-        <v>1140044400000</v>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>15/02/06</t>
+        </is>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
@@ -18096,8 +18530,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I194" t="n">
-        <v>1213740000000</v>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>17/06/08</t>
+        </is>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
@@ -18187,8 +18623,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I195" t="n">
-        <v>1213740000000</v>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>17/06/08</t>
+        </is>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
@@ -18278,8 +18716,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I196" t="n">
-        <v>1416351600000</v>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>18/11/14</t>
+        </is>
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
@@ -18369,8 +18809,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I197" t="n">
-        <v>730940400000</v>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>28/02/93</t>
+        </is>
       </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
@@ -18456,8 +18898,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I198" t="n">
-        <v>796687200000</v>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>31/03/95</t>
+        </is>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
@@ -18543,8 +18987,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I199" t="n">
-        <v>1038956400000</v>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>03/12/02</t>
+        </is>
       </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
@@ -18630,8 +19076,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I200" t="n">
-        <v>715298400000</v>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>31/08/92</t>
+        </is>
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
@@ -18717,8 +19165,10 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="I201" t="n">
-        <v>715298400000</v>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>31/08/92</t>
+        </is>
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
